--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/117.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/117.xlsx
@@ -426,13 +426,13 @@
         <v>-18.72773757983131</v>
       </c>
       <c r="E2">
-        <v>-17.58482290365088</v>
+        <v>-13.25763503714746</v>
       </c>
       <c r="F2">
-        <v>-0.1766122193613764</v>
+        <v>-0.09608745250263921</v>
       </c>
       <c r="G2">
-        <v>-13.01602404351808</v>
+        <v>-10.78200106354859</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-18.43188483348372</v>
       </c>
       <c r="E3">
-        <v>-18.88578103047045</v>
+        <v>-15.11262025948745</v>
       </c>
       <c r="F3">
-        <v>0.03891821007081862</v>
+        <v>-0.2725959786911579</v>
       </c>
       <c r="G3">
-        <v>-12.7979770272283</v>
+        <v>-9.239941773364151</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-18.07753857367524</v>
       </c>
       <c r="E4">
-        <v>-19.46519022280386</v>
+        <v>-15.18729026739993</v>
       </c>
       <c r="F4">
-        <v>-0.07747155185952592</v>
+        <v>-0.2021143382239619</v>
       </c>
       <c r="G4">
-        <v>-12.32352551461883</v>
+        <v>-9.183875540577919</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-17.68638263425487</v>
       </c>
       <c r="E5">
-        <v>-19.60239392828825</v>
+        <v>-15.22158440106001</v>
       </c>
       <c r="F5">
-        <v>-0.1853456968890915</v>
+        <v>-0.233448163602256</v>
       </c>
       <c r="G5">
-        <v>-12.25284143978527</v>
+        <v>-8.294772778279864</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-17.27315628394883</v>
       </c>
       <c r="E6">
-        <v>-19.20328140009624</v>
+        <v>-15.43224901189684</v>
       </c>
       <c r="F6">
-        <v>0.008357251479336461</v>
+        <v>-0.145634591966286</v>
       </c>
       <c r="G6">
-        <v>-12.11875432075857</v>
+        <v>-8.147124370547971</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-16.85912083537643</v>
       </c>
       <c r="E7">
-        <v>-20.82672574642404</v>
+        <v>-17.93141871877595</v>
       </c>
       <c r="F7">
-        <v>0.1339029583128239</v>
+        <v>0.1982190602009831</v>
       </c>
       <c r="G7">
-        <v>-11.24126380155939</v>
+        <v>-8.072755483903155</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-16.44265128384576</v>
       </c>
       <c r="E8">
-        <v>-21.51080155849673</v>
+        <v>-17.88843897196915</v>
       </c>
       <c r="F8">
-        <v>0.1178508547813751</v>
+        <v>0.2185488530004886</v>
       </c>
       <c r="G8">
-        <v>-10.68994639269837</v>
+        <v>-8.189767125934514</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-16.03585635198106</v>
       </c>
       <c r="E9">
-        <v>-21.73351643866796</v>
+        <v>-17.27386165049217</v>
       </c>
       <c r="F9">
-        <v>0.1821073142165328</v>
+        <v>0.140220088126573</v>
       </c>
       <c r="G9">
-        <v>-10.23676375823722</v>
+        <v>-6.883913132149825</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-15.63118285365725</v>
       </c>
       <c r="E10">
-        <v>-22.5281413582159</v>
+        <v>-17.72280097819059</v>
       </c>
       <c r="F10">
-        <v>0.2967864974600963</v>
+        <v>0.3162597583651071</v>
       </c>
       <c r="G10">
-        <v>-10.03484394591211</v>
+        <v>-6.854818540582229</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-15.22333546017906</v>
       </c>
       <c r="E11">
-        <v>-23.52344560341376</v>
+        <v>-19.25614680566178</v>
       </c>
       <c r="F11">
-        <v>0.3741982596191129</v>
+        <v>0.2301592505181265</v>
       </c>
       <c r="G11">
-        <v>-10.00783293003476</v>
+        <v>-6.261058530849791</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-14.81381275412376</v>
       </c>
       <c r="E12">
-        <v>-23.9376877632654</v>
+        <v>-18.31018934172551</v>
       </c>
       <c r="F12">
-        <v>0.2647899781595626</v>
+        <v>0.1737623410007305</v>
       </c>
       <c r="G12">
-        <v>-9.157474831910628</v>
+        <v>-5.855296110365739</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-14.38839620075091</v>
       </c>
       <c r="E13">
-        <v>-23.78019196575264</v>
+        <v>-21.02284037027422</v>
       </c>
       <c r="F13">
-        <v>0.5376508871721085</v>
+        <v>0.8120956346588072</v>
       </c>
       <c r="G13">
-        <v>-8.618173256400294</v>
+        <v>-5.523213519999017</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-13.95860027764561</v>
       </c>
       <c r="E14">
-        <v>-25.4355529968865</v>
+        <v>-20.95406643551973</v>
       </c>
       <c r="F14">
-        <v>0.6357809464425436</v>
+        <v>0.5968128870800492</v>
       </c>
       <c r="G14">
-        <v>-8.240160126644465</v>
+        <v>-5.25640427011433</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-13.52567959058763</v>
       </c>
       <c r="E15">
-        <v>-25.85070990848769</v>
+        <v>-22.03455580527586</v>
       </c>
       <c r="F15">
-        <v>1.06679044652796</v>
+        <v>0.7015491763878103</v>
       </c>
       <c r="G15">
-        <v>-8.642057268131492</v>
+        <v>-3.966513419216339</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-13.09249007016293</v>
       </c>
       <c r="E16">
-        <v>-27.83715220279634</v>
+        <v>-23.00137594896547</v>
       </c>
       <c r="F16">
-        <v>1.267631436806311</v>
+        <v>1.278044015059501</v>
       </c>
       <c r="G16">
-        <v>-7.814211631126709</v>
+        <v>-5.392719338579901</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-12.67232216303604</v>
       </c>
       <c r="E17">
-        <v>-28.25013544687385</v>
+        <v>-23.55898959589996</v>
       </c>
       <c r="F17">
-        <v>1.420249847098092</v>
+        <v>1.212038043669631</v>
       </c>
       <c r="G17">
-        <v>-8.485234564919391</v>
+        <v>-4.175353327810317</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-12.26583261310172</v>
       </c>
       <c r="E18">
-        <v>-28.16408991225411</v>
+        <v>-26.05093638673684</v>
       </c>
       <c r="F18">
-        <v>1.679205780887246</v>
+        <v>1.728170578066724</v>
       </c>
       <c r="G18">
-        <v>-7.658448762478309</v>
+        <v>-4.673012920509738</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-11.8868890606368</v>
       </c>
       <c r="E19">
-        <v>-29.33546122687018</v>
+        <v>-25.8828892447862</v>
       </c>
       <c r="F19">
-        <v>2.107271263223113</v>
+        <v>1.629593200398778</v>
       </c>
       <c r="G19">
-        <v>-8.14334440331149</v>
+        <v>-3.83172083755435</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-11.54868765299805</v>
       </c>
       <c r="E20">
-        <v>-30.98018260832302</v>
+        <v>-26.81125811567668</v>
       </c>
       <c r="F20">
-        <v>2.522801890019817</v>
+        <v>2.399042143306766</v>
       </c>
       <c r="G20">
-        <v>-7.690821294383791</v>
+        <v>-3.947055775368832</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-11.25452402715104</v>
       </c>
       <c r="E21">
-        <v>-30.71430684238468</v>
+        <v>-28.18611640982742</v>
       </c>
       <c r="F21">
-        <v>2.49958937865857</v>
+        <v>2.846047417940241</v>
       </c>
       <c r="G21">
-        <v>-7.56951453333112</v>
+        <v>-3.973443359149886</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-11.01595521060885</v>
       </c>
       <c r="E22">
-        <v>-31.0731567081745</v>
+        <v>-28.11533183261352</v>
       </c>
       <c r="F22">
-        <v>2.52521409589677</v>
+        <v>2.665493145356449</v>
       </c>
       <c r="G22">
-        <v>-7.071438225493649</v>
+        <v>-4.890436504703223</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-10.82835754722486</v>
       </c>
       <c r="E23">
-        <v>-31.20428999425162</v>
+        <v>-28.73907478548202</v>
       </c>
       <c r="F23">
-        <v>2.666793682178844</v>
+        <v>3.342514510194874</v>
       </c>
       <c r="G23">
-        <v>-7.454950682583108</v>
+        <v>-4.736347059050139</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-10.684099372415</v>
       </c>
       <c r="E24">
-        <v>-31.87839637079642</v>
+        <v>-28.62078198745366</v>
       </c>
       <c r="F24">
-        <v>3.120326491946379</v>
+        <v>3.473010540627491</v>
       </c>
       <c r="G24">
-        <v>-7.763011449913134</v>
+        <v>-4.377269858913866</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-10.57307011464322</v>
       </c>
       <c r="E25">
-        <v>-32.3842812591413</v>
+        <v>-28.72488254794198</v>
       </c>
       <c r="F25">
-        <v>3.014134761111899</v>
+        <v>3.429228009919926</v>
       </c>
       <c r="G25">
-        <v>-7.305940567904044</v>
+        <v>-5.163079766520603</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-10.46836027119502</v>
       </c>
       <c r="E26">
-        <v>-31.68105000201616</v>
+        <v>-28.65500366552962</v>
       </c>
       <c r="F26">
-        <v>3.366144518727133</v>
+        <v>3.366731002848315</v>
       </c>
       <c r="G26">
-        <v>-7.625347799386631</v>
+        <v>-4.835594167558663</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-10.35807281017268</v>
       </c>
       <c r="E27">
-        <v>-31.8074759393623</v>
+        <v>-28.5074523969377</v>
       </c>
       <c r="F27">
-        <v>3.268072445174893</v>
+        <v>3.609666311067325</v>
       </c>
       <c r="G27">
-        <v>-7.253034151479558</v>
+        <v>-4.344221395367139</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-10.22328330509304</v>
       </c>
       <c r="E28">
-        <v>-33.05612113444526</v>
+        <v>-27.86234863217502</v>
       </c>
       <c r="F28">
-        <v>2.966250155025671</v>
+        <v>3.164094112040694</v>
       </c>
       <c r="G28">
-        <v>-7.339205592073695</v>
+        <v>-5.696931233020699</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-10.04906891150405</v>
       </c>
       <c r="E29">
-        <v>-31.59312741492024</v>
+        <v>-28.83711171927408</v>
       </c>
       <c r="F29">
-        <v>3.030947305919118</v>
+        <v>2.982303915291926</v>
       </c>
       <c r="G29">
-        <v>-7.716831537685509</v>
+        <v>-4.691929162799936</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-9.831699397420198</v>
       </c>
       <c r="E30">
-        <v>-31.09767839492604</v>
+        <v>-28.51685803745163</v>
       </c>
       <c r="F30">
-        <v>3.220825681988821</v>
+        <v>3.590907102863528</v>
       </c>
       <c r="G30">
-        <v>-7.133581280607973</v>
+        <v>-4.964126178485232</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-9.5642189858847</v>
       </c>
       <c r="E31">
-        <v>-31.41597351174017</v>
+        <v>-28.12646735019838</v>
       </c>
       <c r="F31">
-        <v>2.886836228854088</v>
+        <v>2.895948270284883</v>
       </c>
       <c r="G31">
-        <v>-7.626548726477387</v>
+        <v>-3.864851331640063</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-9.25621154080695</v>
       </c>
       <c r="E32">
-        <v>-30.42902656532347</v>
+        <v>-27.75928962070845</v>
       </c>
       <c r="F32">
-        <v>3.039873793051686</v>
+        <v>3.135192373357019</v>
       </c>
       <c r="G32">
-        <v>-7.472328031961927</v>
+        <v>-4.820520235714574</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-8.920904230436228</v>
       </c>
       <c r="E33">
-        <v>-30.06308963771164</v>
+        <v>-26.68799305318789</v>
       </c>
       <c r="F33">
-        <v>2.936195328917299</v>
+        <v>2.909268418121899</v>
       </c>
       <c r="G33">
-        <v>-6.893464768109368</v>
+        <v>-3.946205938984936</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-8.571911475687806</v>
       </c>
       <c r="E34">
-        <v>-30.43331276597173</v>
+        <v>-27.57943221854581</v>
       </c>
       <c r="F34">
-        <v>2.937794078004702</v>
+        <v>2.303122168267</v>
       </c>
       <c r="G34">
-        <v>-7.144593060161469</v>
+        <v>-4.471060295969034</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-8.232155233423043</v>
       </c>
       <c r="E35">
-        <v>-30.05321303590092</v>
+        <v>-26.57341360384581</v>
       </c>
       <c r="F35">
-        <v>2.43895122803884</v>
+        <v>2.629001904528325</v>
       </c>
       <c r="G35">
-        <v>-7.364556309841965</v>
+        <v>-3.845328063361367</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-7.915495156686289</v>
       </c>
       <c r="E36">
-        <v>-29.51177736235883</v>
+        <v>-27.60677514460412</v>
       </c>
       <c r="F36">
-        <v>2.40137813938266</v>
+        <v>2.540494161008809</v>
       </c>
       <c r="G36">
-        <v>-6.381561392620398</v>
+        <v>-3.744653623474484</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-7.635337712366131</v>
       </c>
       <c r="E37">
-        <v>-28.26212231757216</v>
+        <v>-25.25897420990541</v>
       </c>
       <c r="F37">
-        <v>2.339785709514906</v>
+        <v>2.644429419038063</v>
       </c>
       <c r="G37">
-        <v>-6.943477147118425</v>
+        <v>-4.010629443083073</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-7.403321951619169</v>
       </c>
       <c r="E38">
-        <v>-28.63725204741955</v>
+        <v>-25.167816028131</v>
       </c>
       <c r="F38">
-        <v>2.427050901930222</v>
+        <v>2.708647773572692</v>
       </c>
       <c r="G38">
-        <v>-7.392633722726133</v>
+        <v>-3.894694041723213</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-7.21680296927367</v>
       </c>
       <c r="E39">
-        <v>-27.6846920683801</v>
+        <v>-23.31170321576311</v>
       </c>
       <c r="F39">
-        <v>2.376454220967229</v>
+        <v>2.701949594753655</v>
       </c>
       <c r="G39">
-        <v>-7.181063837794698</v>
+        <v>-4.413314077744366</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-7.078083942365684</v>
       </c>
       <c r="E40">
-        <v>-27.90168748587965</v>
+        <v>-24.71809327442926</v>
       </c>
       <c r="F40">
-        <v>2.780687573124554</v>
+        <v>2.536915613828715</v>
       </c>
       <c r="G40">
-        <v>-6.894376947702894</v>
+        <v>-3.99031868163011</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-6.978829051530289</v>
       </c>
       <c r="E41">
-        <v>-27.50356669349531</v>
+        <v>-22.93227143560842</v>
       </c>
       <c r="F41">
-        <v>2.361532010573198</v>
+        <v>2.37293034603572</v>
       </c>
       <c r="G41">
-        <v>-7.174580143993235</v>
+        <v>-3.338271052115697</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-6.908919969804656</v>
       </c>
       <c r="E42">
-        <v>-26.19902654373567</v>
+        <v>-24.35142273402819</v>
       </c>
       <c r="F42">
-        <v>2.463434454995983</v>
+        <v>2.468868545158347</v>
       </c>
       <c r="G42">
-        <v>-6.82000149861496</v>
+        <v>-3.398022096713185</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-6.860783155784366</v>
       </c>
       <c r="E43">
-        <v>-26.24400787605386</v>
+        <v>-22.24767484902485</v>
       </c>
       <c r="F43">
-        <v>2.484498181314368</v>
+        <v>2.632969784387735</v>
       </c>
       <c r="G43">
-        <v>-7.010679845877411</v>
+        <v>-2.877846761672855</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-6.8176204144225</v>
       </c>
       <c r="E44">
-        <v>-25.4052710911972</v>
+        <v>-22.20251690622036</v>
       </c>
       <c r="F44">
-        <v>2.498572143487932</v>
+        <v>2.595885432499207</v>
       </c>
       <c r="G44">
-        <v>-6.967459595496406</v>
+        <v>-2.796895744579794</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-6.771296719084805</v>
       </c>
       <c r="E45">
-        <v>-25.2756208803576</v>
+        <v>-21.55626743753374</v>
       </c>
       <c r="F45">
-        <v>2.734938498202743</v>
+        <v>2.80353560282857</v>
       </c>
       <c r="G45">
-        <v>-7.104027318022054</v>
+        <v>-2.956773265063738</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-6.711852354620476</v>
       </c>
       <c r="E46">
-        <v>-24.80537055397909</v>
+        <v>-20.90196181358747</v>
       </c>
       <c r="F46">
-        <v>2.806067093611525</v>
+        <v>2.266377447013619</v>
       </c>
       <c r="G46">
-        <v>-7.29674658509448</v>
+        <v>-3.70851753044032</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-6.629834493717603</v>
       </c>
       <c r="E47">
-        <v>-24.35850073890218</v>
+        <v>-20.85873752918426</v>
       </c>
       <c r="F47">
-        <v>2.230048566196444</v>
+        <v>2.503260702987777</v>
       </c>
       <c r="G47">
-        <v>-7.252525562137844</v>
+        <v>-3.288934604747886</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-6.524521938650764</v>
       </c>
       <c r="E48">
-        <v>-23.32871216413591</v>
+        <v>-19.71310153235377</v>
       </c>
       <c r="F48">
-        <v>2.696840224613188</v>
+        <v>2.569516841333293</v>
       </c>
       <c r="G48">
-        <v>-7.186412228936592</v>
+        <v>-4.380311551299472</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-6.39375879094173</v>
       </c>
       <c r="E49">
-        <v>-23.28400254025819</v>
+        <v>-20.93807639379864</v>
       </c>
       <c r="F49">
-        <v>2.425072760572337</v>
+        <v>2.868371919445687</v>
       </c>
       <c r="G49">
-        <v>-7.206657365958367</v>
+        <v>-3.659866858378433</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-6.241072482563864</v>
       </c>
       <c r="E50">
-        <v>-22.47265396619992</v>
+        <v>-19.5002813678893</v>
       </c>
       <c r="F50">
-        <v>2.776338644259857</v>
+        <v>2.242954530332061</v>
       </c>
       <c r="G50">
-        <v>-7.182169609460231</v>
+        <v>-4.14265267374889</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-6.075822002881641</v>
       </c>
       <c r="E51">
-        <v>-22.41440873351326</v>
+        <v>-19.62718732348025</v>
       </c>
       <c r="F51">
-        <v>2.692433310030295</v>
+        <v>2.404231036717902</v>
       </c>
       <c r="G51">
-        <v>-7.48206013510724</v>
+        <v>-3.146076780492782</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-5.904220660286883</v>
       </c>
       <c r="E52">
-        <v>-22.34733297651165</v>
+        <v>-17.66632637884093</v>
       </c>
       <c r="F52">
-        <v>2.599591548259331</v>
+        <v>2.868037259014956</v>
       </c>
       <c r="G52">
-        <v>-6.629437994107089</v>
+        <v>-3.722744907122072</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-5.740683536284496</v>
       </c>
       <c r="E53">
-        <v>-21.85808570167096</v>
+        <v>-17.90402145102954</v>
       </c>
       <c r="F53">
-        <v>2.915779385907903</v>
+        <v>2.653949017231035</v>
       </c>
       <c r="G53">
-        <v>-7.733155614943747</v>
+        <v>-4.201455445315699</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-5.597193033994071</v>
       </c>
       <c r="E54">
-        <v>-21.31995807839148</v>
+        <v>-17.10275778858636</v>
       </c>
       <c r="F54">
-        <v>2.733459034021343</v>
+        <v>2.475179048032874</v>
       </c>
       <c r="G54">
-        <v>-7.852152396018568</v>
+        <v>-4.168393856882735</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-5.483613464754613</v>
       </c>
       <c r="E55">
-        <v>-20.10313447016041</v>
+        <v>-17.93710195365557</v>
       </c>
       <c r="F55">
-        <v>2.653079231458096</v>
+        <v>2.526986802138761</v>
       </c>
       <c r="G55">
-        <v>-7.922065383785657</v>
+        <v>-5.210483574389901</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-5.412682523589042</v>
       </c>
       <c r="E56">
-        <v>-20.53382404760792</v>
+        <v>-16.2235772023672</v>
       </c>
       <c r="F56">
-        <v>2.750163891066198</v>
+        <v>2.741292076182215</v>
       </c>
       <c r="G56">
-        <v>-7.657703925184316</v>
+        <v>-4.988571279103095</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-5.38710950553184</v>
       </c>
       <c r="E57">
-        <v>-20.08467641010515</v>
+        <v>-18.35521595878378</v>
       </c>
       <c r="F57">
-        <v>2.806019048302163</v>
+        <v>2.944265284155372</v>
       </c>
       <c r="G57">
-        <v>-8.33409165622669</v>
+        <v>-5.022148019320893</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-5.410874732450799</v>
       </c>
       <c r="E58">
-        <v>-18.84355753882293</v>
+        <v>-16.8056446089431</v>
       </c>
       <c r="F58">
-        <v>3.052136944082729</v>
+        <v>2.828085099177936</v>
       </c>
       <c r="G58">
-        <v>-8.035159247275038</v>
+        <v>-5.101763579239259</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-5.482756254489442</v>
       </c>
       <c r="E59">
-        <v>-19.87767533474053</v>
+        <v>-16.48258780170991</v>
       </c>
       <c r="F59">
-        <v>2.932971322985604</v>
+        <v>2.744653591102775</v>
       </c>
       <c r="G59">
-        <v>-8.284085839660753</v>
+        <v>-4.053560945966848</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-5.593329002300456</v>
       </c>
       <c r="E60">
-        <v>-18.9031658421859</v>
+        <v>-14.7431284797796</v>
       </c>
       <c r="F60">
-        <v>2.886100638600402</v>
+        <v>3.07307475855589</v>
       </c>
       <c r="G60">
-        <v>-8.521610187127395</v>
+        <v>-4.560257022840979</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-5.735508794553243</v>
       </c>
       <c r="E61">
-        <v>-19.55540195351066</v>
+        <v>-16.27620712728434</v>
       </c>
       <c r="F61">
-        <v>2.867291728352436</v>
+        <v>2.524007992958293</v>
       </c>
       <c r="G61">
-        <v>-8.833408265813629</v>
+        <v>-5.008435794423973</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-5.898138903747166</v>
       </c>
       <c r="E62">
-        <v>-18.49747344126073</v>
+        <v>-13.56773588024471</v>
       </c>
       <c r="F62">
-        <v>2.664840391843043</v>
+        <v>3.352300842691547</v>
       </c>
       <c r="G62">
-        <v>-9.418683036593343</v>
+        <v>-4.929305855296405</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-6.068985014230405</v>
       </c>
       <c r="E63">
-        <v>-17.05058976801799</v>
+        <v>-14.76301753762129</v>
       </c>
       <c r="F63">
-        <v>2.990146897861631</v>
+        <v>2.762637447417553</v>
       </c>
       <c r="G63">
-        <v>-9.181116033246427</v>
+        <v>-5.509018955532859</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-6.239484155507816</v>
       </c>
       <c r="E64">
-        <v>-17.8073475879138</v>
+        <v>-15.50540650949075</v>
       </c>
       <c r="F64">
-        <v>2.814024390882817</v>
+        <v>3.07820566624883</v>
       </c>
       <c r="G64">
-        <v>-8.946377442883751</v>
+        <v>-6.18471763004775</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-6.396019729310829</v>
       </c>
       <c r="E65">
-        <v>-17.90523961053761</v>
+        <v>-13.98128971204719</v>
       </c>
       <c r="F65">
-        <v>2.875795748109576</v>
+        <v>2.543858989398981</v>
       </c>
       <c r="G65">
-        <v>-9.826023724647488</v>
+        <v>-6.396884697303005</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-6.530947850182616</v>
       </c>
       <c r="E66">
-        <v>-18.43580468222428</v>
+        <v>-13.72070320374981</v>
       </c>
       <c r="F66">
-        <v>2.984856943627354</v>
+        <v>2.920229375595742</v>
       </c>
       <c r="G66">
-        <v>-9.660577971177167</v>
+        <v>-6.487279070044147</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-6.636804398522952</v>
       </c>
       <c r="E67">
-        <v>-17.81506410762287</v>
+        <v>-14.58527946129423</v>
       </c>
       <c r="F67">
-        <v>2.541180049218327</v>
+        <v>2.70005429013605</v>
       </c>
       <c r="G67">
-        <v>-9.937998691585099</v>
+        <v>-5.655305656317583</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-6.706019691623575</v>
       </c>
       <c r="E68">
-        <v>-17.90227798853659</v>
+        <v>-15.14720874395804</v>
       </c>
       <c r="F68">
-        <v>2.487208599456328</v>
+        <v>2.563299115607879</v>
       </c>
       <c r="G68">
-        <v>-10.20253733615065</v>
+        <v>-5.721373052417002</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-6.737594242681956</v>
       </c>
       <c r="E69">
-        <v>-18.25607407733385</v>
+        <v>-13.76365125123856</v>
       </c>
       <c r="F69">
-        <v>2.413495497750811</v>
+        <v>2.175833576418022</v>
       </c>
       <c r="G69">
-        <v>-9.610782152791034</v>
+        <v>-5.584936578753732</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-6.725770826738197</v>
       </c>
       <c r="E70">
-        <v>-16.87790999715751</v>
+        <v>-13.70541507549992</v>
       </c>
       <c r="F70">
-        <v>2.347960039045731</v>
+        <v>2.351871589921751</v>
       </c>
       <c r="G70">
-        <v>-9.669575080693164</v>
+        <v>-6.514139149729762</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-6.67154261702596</v>
       </c>
       <c r="E71">
-        <v>-17.4736624521846</v>
+        <v>-13.20456585025157</v>
       </c>
       <c r="F71">
-        <v>1.954290028008905</v>
+        <v>2.242507211934549</v>
       </c>
       <c r="G71">
-        <v>-9.289639155103501</v>
+        <v>-6.335158357326731</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-6.575471005183958</v>
       </c>
       <c r="E72">
-        <v>-16.65510001903211</v>
+        <v>-14.76171333710708</v>
       </c>
       <c r="F72">
-        <v>1.961970650567662</v>
+        <v>2.421369958281824</v>
       </c>
       <c r="G72">
-        <v>-9.856870488527829</v>
+        <v>-6.513223688914676</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-6.438664655466315</v>
       </c>
       <c r="E73">
-        <v>-17.21983695558066</v>
+        <v>-14.40398653287116</v>
       </c>
       <c r="F73">
-        <v>1.648625769845499</v>
+        <v>1.960340423518953</v>
       </c>
       <c r="G73">
-        <v>-9.872128168779247</v>
+        <v>-5.738753683017381</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-6.266966905443909</v>
       </c>
       <c r="E74">
-        <v>-17.33465188557114</v>
+        <v>-15.63536918503688</v>
       </c>
       <c r="F74">
-        <v>2.038334527962138</v>
+        <v>1.484078868953405</v>
       </c>
       <c r="G74">
-        <v>-9.802589240269935</v>
+        <v>-4.879057228335069</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-6.061537242690552</v>
       </c>
       <c r="E75">
-        <v>-17.71774267272402</v>
+        <v>-13.87280106024543</v>
       </c>
       <c r="F75">
-        <v>1.64189445633035</v>
+        <v>1.838951464312714</v>
       </c>
       <c r="G75">
-        <v>-9.387537681551095</v>
+        <v>-5.983611560669384</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-5.829018292090447</v>
       </c>
       <c r="E76">
-        <v>-17.52274205347973</v>
+        <v>-14.95177339120901</v>
       </c>
       <c r="F76">
-        <v>1.695014344402271</v>
+        <v>1.297610053113625</v>
       </c>
       <c r="G76">
-        <v>-9.043990503055673</v>
+        <v>-5.708835504838365</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-5.573763762879967</v>
       </c>
       <c r="E77">
-        <v>-18.79799203335775</v>
+        <v>-15.32381017330916</v>
       </c>
       <c r="F77">
-        <v>1.504037553156457</v>
+        <v>2.081480872504353</v>
       </c>
       <c r="G77">
-        <v>-8.862847385644967</v>
+        <v>-4.691807757602237</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-5.297812885145757</v>
       </c>
       <c r="E78">
-        <v>-18.6290482535536</v>
+        <v>-15.40165916997502</v>
       </c>
       <c r="F78">
-        <v>1.66480875542659</v>
+        <v>1.527139063285729</v>
       </c>
       <c r="G78">
-        <v>-8.737114256708606</v>
+        <v>-5.298082346362396</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-5.00763864657788</v>
       </c>
       <c r="E79">
-        <v>-18.83387566139453</v>
+        <v>-15.2205156811942</v>
       </c>
       <c r="F79">
-        <v>1.218785924532836</v>
+        <v>1.547808486720383</v>
       </c>
       <c r="G79">
-        <v>-8.683449878103888</v>
+        <v>-4.476333219015062</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-4.702398937716247</v>
       </c>
       <c r="E80">
-        <v>-18.9417212698872</v>
+        <v>-14.92700716686106</v>
       </c>
       <c r="F80">
-        <v>0.8846423950611823</v>
+        <v>1.368617706881599</v>
       </c>
       <c r="G80">
-        <v>-8.080384324028865</v>
+        <v>-4.398249989564956</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-4.38636747855865</v>
       </c>
       <c r="E81">
-        <v>-20.05084418079384</v>
+        <v>-15.73151321669373</v>
       </c>
       <c r="F81">
-        <v>1.339667922888562</v>
+        <v>1.272056575472066</v>
       </c>
       <c r="G81">
-        <v>-7.720680410574738</v>
+        <v>-3.971832279364199</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-4.061749438341606</v>
       </c>
       <c r="E82">
-        <v>-19.92714891327433</v>
+        <v>-16.70912471394362</v>
       </c>
       <c r="F82">
-        <v>1.358109038009685</v>
+        <v>1.206317338385897</v>
       </c>
       <c r="G82">
-        <v>-7.24847653473349</v>
+        <v>-3.872063456627723</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-3.726376682216687</v>
       </c>
       <c r="E83">
-        <v>-21.6888430425823</v>
+        <v>-16.70848619910853</v>
       </c>
       <c r="F83">
-        <v>1.127546225318887</v>
+        <v>1.263907096963325</v>
       </c>
       <c r="G83">
-        <v>-7.246950766708347</v>
+        <v>-4.052970326086148</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-3.386795721848005</v>
       </c>
       <c r="E84">
-        <v>-21.38813425457695</v>
+        <v>-18.82683388431261</v>
       </c>
       <c r="F84">
-        <v>0.7350094208890908</v>
+        <v>0.579870288590591</v>
       </c>
       <c r="G84">
-        <v>-7.031476228121172</v>
+        <v>-3.555651980428909</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-3.041735151196755</v>
       </c>
       <c r="E85">
-        <v>-22.33832131323638</v>
+        <v>-17.8147878707084</v>
       </c>
       <c r="F85">
-        <v>0.6142152294780613</v>
+        <v>0.4055743317349498</v>
       </c>
       <c r="G85">
-        <v>-6.409789741696301</v>
+        <v>-3.705377401407931</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-2.695223138447883</v>
       </c>
       <c r="E86">
-        <v>-23.21664148939409</v>
+        <v>-19.90373670265467</v>
       </c>
       <c r="F86">
-        <v>0.6873782952281192</v>
+        <v>-0.05573104937305289</v>
       </c>
       <c r="G86">
-        <v>-6.540756419019977</v>
+        <v>-3.324211017733476</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-2.351988623823757</v>
       </c>
       <c r="E87">
-        <v>-24.48624899065856</v>
+        <v>-20.51074694406483</v>
       </c>
       <c r="F87">
-        <v>0.1611868954588312</v>
+        <v>-0.04292945953018933</v>
       </c>
       <c r="G87">
-        <v>-6.448327688911979</v>
+        <v>-3.206073916707229</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-2.012201774351767</v>
       </c>
       <c r="E88">
-        <v>-25.36549297551383</v>
+        <v>-23.58880054029246</v>
       </c>
       <c r="F88">
-        <v>0.1134207459112034</v>
+        <v>-0.1477079955754932</v>
       </c>
       <c r="G88">
-        <v>-5.360379618890014</v>
+        <v>-2.475080096472575</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-1.685035433590654</v>
       </c>
       <c r="E89">
-        <v>-27.74836241292795</v>
+        <v>-23.53230329857276</v>
       </c>
       <c r="F89">
-        <v>0.1439452563369623</v>
+        <v>-0.3469419530924135</v>
       </c>
       <c r="G89">
-        <v>-5.81321444386586</v>
+        <v>-1.795594892278086</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-1.374101311948309</v>
       </c>
       <c r="E90">
-        <v>-28.04331098199553</v>
+        <v>-25.62116156103888</v>
       </c>
       <c r="F90">
-        <v>-0.2508223415085729</v>
+        <v>-0.4015769251440549</v>
       </c>
       <c r="G90">
-        <v>-4.920413744870309</v>
+        <v>-1.755134149228573</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-1.085137708289668</v>
       </c>
       <c r="E91">
-        <v>-30.05228469872934</v>
+        <v>-27.06027437288446</v>
       </c>
       <c r="F91">
-        <v>-0.6649381167812961</v>
+        <v>-1.156363765022492</v>
       </c>
       <c r="G91">
-        <v>-5.366253005481419</v>
+        <v>-1.424672482312217</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-0.8263582694816505</v>
       </c>
       <c r="E92">
-        <v>-31.83670950331881</v>
+        <v>-28.90414672000962</v>
       </c>
       <c r="F92">
-        <v>-0.6569153784851829</v>
+        <v>-1.046217408207047</v>
       </c>
       <c r="G92">
-        <v>-5.212783710703071</v>
+        <v>-1.738626323563006</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-0.6014626929537777</v>
       </c>
       <c r="E93">
-        <v>-32.93843968040793</v>
+        <v>-30.47546153779813</v>
       </c>
       <c r="F93">
-        <v>-1.385728758448841</v>
+        <v>-1.922452021377322</v>
       </c>
       <c r="G93">
-        <v>-4.749399758413611</v>
+        <v>-2.209002558995644</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-0.41838661933321</v>
       </c>
       <c r="E94">
-        <v>-35.23217742816608</v>
+        <v>-31.54641394129411</v>
       </c>
       <c r="F94">
-        <v>-1.57440765851929</v>
+        <v>-1.855697205855321</v>
       </c>
       <c r="G94">
-        <v>-5.020228504708617</v>
+        <v>-1.663896502546653</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-0.2812732842243402</v>
       </c>
       <c r="E95">
-        <v>-37.10747964914148</v>
+        <v>-34.71421509964275</v>
       </c>
       <c r="F95">
-        <v>-1.776924436053505</v>
+        <v>-2.119481693235393</v>
       </c>
       <c r="G95">
-        <v>-4.986815825568792</v>
+        <v>-1.668952864969757</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-0.1959401649016039</v>
       </c>
       <c r="E96">
-        <v>-38.89170972934862</v>
+        <v>-36.58741384444158</v>
       </c>
       <c r="F96">
-        <v>-2.043272720545241</v>
+        <v>-2.680037086342415</v>
       </c>
       <c r="G96">
-        <v>-4.92118155071522</v>
+        <v>-2.025493680840579</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-0.1622462302274013</v>
       </c>
       <c r="E97">
-        <v>-41.21880874512127</v>
+        <v>-38.86563251177545</v>
       </c>
       <c r="F97">
-        <v>-2.488645283027798</v>
+        <v>-2.854670188730996</v>
       </c>
       <c r="G97">
-        <v>-5.375266521105214</v>
+        <v>-2.016998598223177</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-0.1870322558115071</v>
       </c>
       <c r="E98">
-        <v>-42.96432263679984</v>
+        <v>-40.7304558438971</v>
       </c>
       <c r="F98">
-        <v>-2.907323705955141</v>
+        <v>-3.496117315456196</v>
       </c>
       <c r="G98">
-        <v>-5.534934043409353</v>
+        <v>-2.075551996951468</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-0.2554974303156257</v>
       </c>
       <c r="E99">
-        <v>-45.21735393170303</v>
+        <v>-43.53888636194503</v>
       </c>
       <c r="F99">
-        <v>-3.080308357212151</v>
+        <v>-3.814584820197271</v>
       </c>
       <c r="G99">
-        <v>-5.753424024609658</v>
+        <v>-1.961303143473163</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-0.382917209310756</v>
       </c>
       <c r="E100">
-        <v>-47.18026174659382</v>
+        <v>-45.49346631313571</v>
       </c>
       <c r="F100">
-        <v>-3.459871271379301</v>
+        <v>-4.321435497845997</v>
       </c>
       <c r="G100">
-        <v>-6.25314422444841</v>
+        <v>-2.721335774508902</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-0.5275922199924835</v>
       </c>
       <c r="E101">
-        <v>-49.05579605186211</v>
+        <v>-48.00579123700711</v>
       </c>
       <c r="F101">
-        <v>-3.66929580468546</v>
+        <v>-4.496616151087828</v>
       </c>
       <c r="G101">
-        <v>-6.143863140411104</v>
+        <v>-2.775781083844768</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-0.7377765398792935</v>
       </c>
       <c r="E102">
-        <v>-51.35953267022919</v>
+        <v>-50.35868217649045</v>
       </c>
       <c r="F102">
-        <v>-3.861911935021415</v>
+        <v>-4.149738957900341</v>
       </c>
       <c r="G102">
-        <v>-6.424496176725732</v>
+        <v>-2.676986783911447</v>
       </c>
     </row>
   </sheetData>
